--- a/ppt_nba.xlsx
+++ b/ppt_nba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[閒聊] 2026/07/13 盤後閒聊</t>
+          <t>[BOX ] Hornets 75:87 Celtics (夏季聯賽)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[情報] 2885 元大金 6月自結 0.56 累計 2.74</t>
+          <t>[BOX ] Thunder 79:104 Warriors (夏季聯賽)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -470,12 +470,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[情報] 5288豐祥-KY 6月營收</t>
+          <t>[Live] 夏季聯盟   國王 VS 巫師</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -487,12 +487,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[新聞] 川普T1手機實測曝！遠落後Google Pixel</t>
+          <t>[BOX ] Magic 112:105 Trail Blazers (夏季聯賽)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[情報] 6869 雲豹能源 115年6月營收</t>
+          <t>Re: [情報] 嘴綠：英雄可能跟普爾一樣不尊重人</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>爆</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -521,12 +521,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[情報] 3661 世芯-KY 6月營收 MoM 84.6%</t>
+          <t>[BOX ] Kings 85:104 Wizards (夏季聯賽)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>無標題</t>
+          <t>[Live] 夏季聯盟     快艇 VS 爵士</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>無標題</t>
+          <t>Re: [新聞] 醜1-NBA》詹皇條件降低了？經紀人曝「他</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>爆</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -572,12 +572,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Re: [標的] 4737 華廣</t>
+          <t>[花邊] 杰倫:球員提升球隊價值，應該要持有股權</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>爆</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[新聞] 記憶體股獲利暴衝密碼曝光 外資集體點讚</t>
+          <t>[BOX ] Spurs 90:80 Bucks (夏季聯賽)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -606,12 +606,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Re: [標的] 4737 華廣</t>
+          <t>[情報] 如LBJ沒加盟熱火 Westbrook可能加盟</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>爆</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -623,12 +623,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[情報] 0713 上市投信買賣超排行</t>
+          <t>[BOX ] Clippers 104:82 Jazz (夏季聯賽)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -640,12 +640,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[情報] 115年07月13日 三大法人買賣金額統計表</t>
+          <t>[新聞] 醜1-NBA》勇士能否搶到詹皇？追夢格林</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -657,12 +657,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[新聞] 法興建議做多台股、做空韓股：因獲利持續</t>
+          <t>無標題</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>無標題</t>
+          <t>Re: [花邊] 杰倫:球員提升球隊價值，應該要持有股權</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>無標題</t>
+          <t>Re: [新聞] 球員工會批「第二層豪華稅門檻」傷害聯盟</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -708,12 +708,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[新聞] OpenAI 挖角蘋果牆角惹官司，一句「LOL」</t>
+          <t>Re: [新聞] 球員工會批「第二層豪華稅門檻」傷害聯盟</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[情報] 8932 智通* 6月營收</t>
+          <t>Re: [新聞] 醜1-NBA》詹皇條件降低了？經紀人曝「他</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Re: [新聞] 韓股熔斷 暫停交易20分鐘！SK海力士</t>
+          <t>Re: [新聞] 球員工會批「第二層豪華稅門檻」傷害聯盟</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -759,17 +759,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[情報] 3481 群創 六月營收</t>
+          <t>[公告] 板規v11.2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7/13</t>
+          <t xml:space="preserve"> 9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>[公告] 選秀情報不限額度/FA相關</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 6/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fw: [公告] 板務部小組長級審判團徵人</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7/06</t>
         </is>
       </c>
     </row>
